--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F27149-13F5-42E4-A5A1-626E2D31AE68}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C001F13-96BC-49F2-90EC-00B5CCF364B1}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
   <sheets>
     <sheet name="airline_financials" sheetId="2" r:id="rId1"/>
@@ -997,7 +997,7 @@
     <col min="8" max="9" width="17.140625" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -12653,9 +12653,9 @@
       <c r="J505">
         <v>27853000000</v>
       </c>
-      <c r="K505" t="e">
-        <f>ROUND($K$219*((D505-F505)/($D$219-$F$219)),0)</f>
-        <v>#DIV/0!</v>
+      <c r="K505">
+        <f>ROUND($K$547*((D505-F505)/($D$547-$F$547)),0)</f>
+        <v>610559</v>
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.25">
@@ -12910,9 +12910,9 @@
       <c r="J516">
         <v>27209000000</v>
       </c>
-      <c r="K516" t="e">
-        <f>ROUND($K$219*((D516-F516)/($D$219-$F$219)),0)</f>
-        <v>#DIV/0!</v>
+      <c r="K516">
+        <f>ROUND($K$547*((D516-F516)/($D$547-$F$547)),0)</f>
+        <v>120716144</v>
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.25">
@@ -13167,9 +13167,9 @@
       <c r="J527">
         <v>25848000000</v>
       </c>
-      <c r="K527" t="e">
-        <f>ROUND($K$219*((D527-F527)/($D$219-$F$219)),0)</f>
-        <v>#DIV/0!</v>
+      <c r="K527">
+        <f>ROUND($K$547*((D527-F527)/($D$547-$F$547)),0)</f>
+        <v>7762816</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
@@ -13407,9 +13407,9 @@
       <c r="J537">
         <v>24617000000</v>
       </c>
-      <c r="K537" t="e">
-        <f>ROUND($K$219*((D537-F537)/($D$219-$F$219)),0)</f>
-        <v>#DIV/0!</v>
+      <c r="K537">
+        <f>ROUND($K$547*((D537-F537)/($D$547-$F$547)),0)</f>
+        <v>98910482</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
@@ -13893,6 +13893,7 @@
         <v>24705000000</v>
       </c>
       <c r="K557">
+        <f>IF(D557-F557&gt;0, ROUND($K$597*((D557-F557)/(IF(($D$557-$F$557)&gt;0, ($D$557-$F$557), 0)+IF(($D$567-$F$567)&gt;0, ($D$567-$F$567), 0)+IF(($D$577-$F$577)&gt;0, ($D$577-$F$577), 0)+IF(($D$587-$F$587)&gt;0, ($D$587-$F$587), 0))),0), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14132,7 +14133,8 @@
         <v>24217000000</v>
       </c>
       <c r="K567">
-        <v>41000000</v>
+        <f>IF(D567-F567&gt;0, ROUND($K$597*((D567-F567)/(IF(($D$557-$F$557)&gt;0, ($D$557-$F$557), 0)+IF(($D$567-$F$567)&gt;0, ($D$567-$F$567), 0)+IF(($D$577-$F$577)&gt;0, ($D$577-$F$577), 0)+IF(($D$587-$F$587)&gt;0, ($D$587-$F$587), 0))),0), 0)</f>
+        <v>35938400</v>
       </c>
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.25">
@@ -14371,7 +14373,8 @@
         <v>24538000000</v>
       </c>
       <c r="K577">
-        <v>0</v>
+        <f>IF(D577-F577&gt;0, ROUND($K$597*((D577-F577)/(IF(($D$557-$F$557)&gt;0, ($D$557-$F$557), 0)+IF(($D$567-$F$567)&gt;0, ($D$567-$F$567), 0)+IF(($D$577-$F$577)&gt;0, ($D$577-$F$577), 0)+IF(($D$587-$F$587)&gt;0, ($D$587-$F$587), 0))),0), 0)</f>
+        <v>4781232</v>
       </c>
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.25">
@@ -14609,9 +14612,9 @@
       <c r="J587">
         <v>24639000000</v>
       </c>
-      <c r="K587" t="e">
-        <f>ROUND($K$241*(((D587-F587)/($D$241-$F$241))/(((D587-F587)/($D$241-$F$241))+((D575-F575)/($D$241-$F$241)))),0)</f>
-        <v>#DIV/0!</v>
+      <c r="K587">
+        <f>IF(D587-F587&gt;0, ROUND($K$597*((D587-F587)/(IF(($D$557-$F$557)&gt;0, ($D$557-$F$557), 0)+IF(($D$567-$F$567)&gt;0, ($D$567-$F$567), 0)+IF(($D$577-$F$577)&gt;0, ($D$577-$F$577), 0)+IF(($D$587-$F$587)&gt;0, ($D$587-$F$587), 0))),0), 0)</f>
+        <v>14280368</v>
       </c>
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.25">
@@ -15095,6 +15098,7 @@
         <v>22934000000</v>
       </c>
       <c r="K607">
+        <f>IF(D607-F607&gt;0, ROUND($K$597*((D607-F607)/(IF(($D$557-$F$557)&gt;0, ($D$557-$F$557), 0)+IF(($D$567-$F$567)&gt;0, ($D$567-$F$567), 0)+IF(($D$577-$F$577)&gt;0, ($D$577-$F$577), 0)+IF(($D$587-$F$587)&gt;0, ($D$587-$F$587), 0))),0), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15314,6 +15318,7 @@
         <v>81843000000</v>
       </c>
       <c r="K616">
+        <f>IF(D616-F616&gt;0, ROUND($K$640*((D616-F616)/(IF(($D$607-$F$607)&gt;0, ($D$607-$F$607), 0)+IF(($D$616-$F$616)&gt;0, ($D$616-$F$616), 0)+IF(($D$624-$F$624)&gt;0, ($D$624-$F$624), 0)+IF(($D$632-$F$632)&gt;0, ($D$632-$F$632), 0))),0), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -15495,7 +15500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>2026</v>
       </c>
@@ -15506,7 +15511,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>2026</v>
       </c>
@@ -15517,7 +15522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>2026</v>
       </c>
@@ -15527,8 +15532,32 @@
       <c r="C627" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D627">
+        <v>20186000000</v>
+      </c>
+      <c r="E627">
+        <v>15534000000</v>
+      </c>
+      <c r="F627">
+        <v>18732000000</v>
+      </c>
+      <c r="G627">
+        <v>756000000</v>
+      </c>
+      <c r="H627">
+        <v>68133000000</v>
+      </c>
+      <c r="I627">
+        <v>79288000000</v>
+      </c>
+      <c r="J627">
+        <v>9124000000</v>
+      </c>
+      <c r="K627">
+        <v>389000000</v>
+      </c>
+    </row>
+    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>2026</v>
       </c>
@@ -15539,7 +15568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>2026</v>
       </c>
@@ -15550,7 +15579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>2026</v>
       </c>
@@ -15561,7 +15590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>2026</v>
       </c>

--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C001F13-96BC-49F2-90EC-00B5CCF364B1}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F546F10-6DEF-46EB-9646-2E6C2968824B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
   <sheets>
     <sheet name="airline_financials" sheetId="2" r:id="rId1"/>
@@ -985,22 +985,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BF35CD-6CF2-4D2E-9294-3A1A732D8FBE}">
   <dimension ref="A1:K631"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="17.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2014</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>2381139000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2014</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>8352000000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2014</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>99000000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>4038973000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2014</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>10419000000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2014</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>29000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2014</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>3784727000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2014</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>2777000000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2014</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2014</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>2289201000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2014</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>8988000000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2014</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>340000000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2014</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>4262774000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2014</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>11386000000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2014</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2014</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>4008507000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2014</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>78000000</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2014</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>3202000000</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2014</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2014</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>2106214000</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2014</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>9582000000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2014</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>384000000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2014</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>4502856000</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2014</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>11752000000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2014</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2014</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>4174397000</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2014</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>103000000</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2014</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>3217000000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2014</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2014</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>2169062000</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2014</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>9156000000</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2014</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>262000000</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2014</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>4269027000</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2014</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>11437000000</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2014</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2014</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>4372511000</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2014</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2014</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>3044000000</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2014</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2014</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>8945616000</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2014</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>36078000000</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2014</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>1085000000</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2014</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>17073630000</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2014</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>44994000000</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2014</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>355000000</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2014</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>16340142000</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2014</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>235000000</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2014</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>12240000000</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2015</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2015</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2526031000</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2015</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>9257000000</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2015</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>136000000</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2015</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>4229686000</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2015</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>11419000000</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2015</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>126000000</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2015</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>4729463000</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2015</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2015</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>2819000000</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2015</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2015</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>2690457000</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2015</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>9949000000</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2015</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>411000000</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2015</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>4441648000</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2015</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>12237000000</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2015</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>182000000</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2015</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>5213299000</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2015</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>195000000</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2015</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>3200000000</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2015</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2015</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2597658000</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2015</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>10368000000</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2015</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>563000000</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2015</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>4663198000</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2015</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>12976000000</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2015</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>177000000</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2015</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>5597997000</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2015</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>257000000</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2015</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>3315000000</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2015</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2015</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>2712464000</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>2015</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>10340000000</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>2015</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>380000000</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2015</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>4391790000</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2015</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>12626000000</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2015</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>136000000</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2015</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>5705397000</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>2015</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>146000000</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2015</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>3357000000</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2015</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2015</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>10526610000</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>2015</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>39914000000</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>2015</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>1490000000</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2015</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>17726322000</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2015</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>49258000000</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2015</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>620000000</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2015</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>21246156000</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2015</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>698000000</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2015</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>12691000000</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2016</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2016</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>3001384000</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2016</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>10453000000</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2016</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>272000000</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2016</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>4368096000</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2016</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>13029000000</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2016</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>155000000</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2016</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>5983005000</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2016</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>94000000</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2016</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>3265000000</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2016</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>98000000</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2016</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>3178904000</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2016</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>11062000000</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2016</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>324000000</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2016</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>4551094000</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2016</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>13597000000</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2016</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>206000000</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2016</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>6419419000</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2016</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>153000000</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2016</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>3689000000</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2016</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>86000000</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2016</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>3121762000</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2016</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>11212000000</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2016</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>326000000</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2016</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>4894768000</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2016</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>13796000000</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2016</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>101000000</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>2016</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>6507204000</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>2016</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>235000000</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>2016</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>3867000000</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>2016</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>57000000</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>2016</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>3073455000</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>2016</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>11408000000</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>2016</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>193000000</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>2016</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>4570679000</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>2016</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>13198000000</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>2016</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>123000000</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>2016</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>6585017000</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>2016</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>145000000</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>2016</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>314000000</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>2016</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>12375505000</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>2016</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>44135000000</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>2016</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>1115000000</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>2016</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>18384637000</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>2016</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>53620000000</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>2016</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>586000000</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>2016</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>25494645000</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>2016</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>628000000</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>2017</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>2017</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>3376837000</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>2017</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>14394000000</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>2017</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>151000000</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>2017</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>4522353000</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>2017</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>13580000000</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>2017</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>99000000</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>2017</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>6875899000</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>2017</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2017</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>94000000</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>2017</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>3584209000</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>2017</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>15612000000</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>2017</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>338000000</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>2017</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>4735491000</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>2017</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>14246000000</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>2017</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>202000000</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>2017</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>7294578000</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>2017</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>140000000</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>2017</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>2017</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>3220246000</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>2017</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>16164000000</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>2017</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>314000000</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>2017</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>4950800000</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>2017</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>14306000000</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>2017</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>2017</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>7681312000</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>2017</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>109000000</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>2017</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>47000000</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>2017</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>3430711000</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>2017</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>15902000000</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>2017</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>262000000</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>2017</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>4798038000</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>2017</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>13875000000</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>2017</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>115000000</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>2017</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>7741030000</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>2017</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>2017</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>241000000</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>2017</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>13612003000</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>2017</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>62072000000</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>2017</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>1065000000</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>2017</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>19006682000</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>2017</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>56007000000</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>2017</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>543000000</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>2017</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>29592819000</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>2017</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>349000000</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>2018</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>29000000</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>2018</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>3728563000</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>2018</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>15480000000</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>2018</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>188000000</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>2018</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>4731498000</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>2018</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>14025000000</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>2018</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>102000000</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>2018</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>8408764000</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>2018</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>17000000</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>2018</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>63000000</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>2018</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>3922294000</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>2018</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>16833000000</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>2018</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>404000000</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>2018</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>5020026000</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>2018</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>15138000000</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>2018</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>166000000</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>2018</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>9515842000</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>2018</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>108000000</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>2018</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>2018</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>3643948000</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>2018</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>16943000000</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>2018</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>399000000</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>2018</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>5352976000</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>2018</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>15551000000</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>2018</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>135000000</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>2018</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>9579448000</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>2018</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>2018</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>2018</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>3605069000</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>2018</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>16079000000</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>2018</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>311000000</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>2018</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>5067411000</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>2018</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>15167000000</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>2018</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>141000000</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>2018</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>8998928000</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>2018</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>82000000</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>2018</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>175000000</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>2018</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>14899874000</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>2018</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>65335000000</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>2018</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>1301000000</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>2018</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>20171911000</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>2018</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>59881000000</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>2018</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>544000000</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>2018</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>36502982000</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>2018</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>334000000</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>2019</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>2019</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>3802132000</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>2019</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>15508000000</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2019</v>
       </c>
@@ -6706,7 +6706,7 @@
         <v>220000000</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>2019</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>4851921000</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>2019</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>15437000000</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>2019</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>88000000</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>2019</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>9829044000</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>2019</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>33000000</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>2019</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>67000000</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>2019</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>4311182000</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>2019</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>16980000000</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>2019</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>518000000</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>2019</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>5157677000</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>2019</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>16029000000</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>2019</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>170000000</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>2019</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>10775878000</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>2019</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>161000000</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>2019</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>52000000</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>2019</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>3687473000</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>2019</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>17519000000</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>2019</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>517000000</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>2019</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>5331914000</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>2019</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>16296000000</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>2019</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>144000000</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>2019</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>10686246000</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>2019</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>174000000</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>2019</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>74000000</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>2019</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>3745031000</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>2019</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>16647000000</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>2019</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>387000000</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>2019</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>5255199000</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>2019</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>16079000000</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>2019</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>264000000</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>2019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>10491833000</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>2019</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>123000000</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>2019</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>213000000</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>2019</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>15545818000</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>2019</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>66654000000</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>2019</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>1643000000</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>2019</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>20596711000</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>2019</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>63841000000</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>2019</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>667000000</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>2019</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>41783001000</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>2019</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>491000000</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>2020</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>2020</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>3964009000</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>2020</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>15304000000</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>2020</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>2020</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>4979529000</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>2020</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>14891000000</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>2020</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>2020</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>10913934000</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>2020</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>1508196000</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>2020</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>2020</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>7140000000</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>2020</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>2020</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>2174683000</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>2020</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>4307000000</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>2020</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>2020</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>409490000</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>2020</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>2413000000</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>2020</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>2020</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>1809874000</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>2020</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>318049000</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>2020</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>2020</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>1549000000</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>2020</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>2020</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>3449339000</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>2020</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>7871000000</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>2020</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>2020</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>718405000</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>2020</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>6905000000</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>2020</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>2020</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>7164634000</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>2020</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>763362000</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>2020</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>2020</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>3986000000</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>2020</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>2020</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>3226049000</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>2020</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>9632000000</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>2020</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>2020</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>1453062000</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>2020</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>8480000000</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>2020</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>2020</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>7829945000</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>2020</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>876634000</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>2020</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>2020</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>4280000000</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>2020</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>2020</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>12814080000</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>2020</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>37114000000</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>2020</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>2020</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>7560486000</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>2020</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>32689000000</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>2020</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>2020</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>27718387000</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>2020</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>3466240000</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>2020</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>2020</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>16955000000</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>2021</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>2021</v>
       </c>
@@ -8960,7 +8960,7 @@
         <v>3921090000</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>2021</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>10397000000</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>2021</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>2021</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>2481647000</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>2021</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>9090000000</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>2021</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>24000000</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>2021</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>7976158000</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>2021</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>1158012000</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>2021</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>2021</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>4592000000</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>2021</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>2021</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>4505786000</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>2021</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>13413000000</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>2021</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>2021</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>3586928000</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>2021</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>13645000000</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>2021</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>85000000</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>2021</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>10226746000</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>2021</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>1198768000</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>2021</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>2021</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>6934000000</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>2021</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>2021</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>4312893000</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>2021</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>14429000000</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>2021</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>2021</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>4229461000</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>2021</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>16168000000</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>2021</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>77000000</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>2021</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>11059710000</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>2021</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>1296555000</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>2021</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>2021</v>
       </c>
@@ -9640,7 +9640,7 @@
         <v>7505000000</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>2021</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>2021</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>4288133000</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>2021</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>14206000000</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>2021</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>2021</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>4237389000</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>2021</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>15210000000</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>2021</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>2021</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>11486720000</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>2021</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>1190868000</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>2021</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>2021</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>7836000000</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>2021</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>2021</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>17027902000</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>2021</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>52445000000</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>2021</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>2021</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>14535425000</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>2021</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>54113000000</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>2021</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>230000000</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>2021</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>40749334000</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>2021</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>4844203000</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>2021</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>2021</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>26867000000</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>2022</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>2022</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>4512315000</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>2022</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>13783000000</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>2022</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>2022</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>4263048000</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>2022</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>15383000000</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>2022</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>37000000</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>2022</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>11718896000</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>2022</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>1684532000</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>2022</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>2022</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>7442000000</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>2022</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>64000000</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>2022</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>4888539000</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>2022</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>15611000000</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>2022</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>2022</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>4516296000</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>2022</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>16405000000</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>2022</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>2022</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>11846547000</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>2022</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>1343116000</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>2022</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>2022</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>7594000000</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>2022</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>59000000</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>2022</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>4315984000</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>2022</v>
       </c>
@@ -10703,7 +10703,7 @@
         <v>16349000000</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>2022</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>237000000</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>2022</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>4964785000</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>2022</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>16217000000</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>2022</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>57000000</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>2022</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>12131033000</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>2022</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>1256755000</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>2022</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>2022</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>8040000000</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>2022</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>88000000</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>2022</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>4192352000</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>2022</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>15030000000</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>2022</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>272000000</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>2022</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>4940513000</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>2022</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>16470000000</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>2022</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>49000000</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>2022</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>12871502000</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>2022</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>1352830000</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>2022</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>2022</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>8670000000</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>2022</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>211000000</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>2022</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>17909190000</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>2022</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>60773000000</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>2022</v>
       </c>
@@ -11229,7 +11229,7 @@
         <v>563000000</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>2022</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>18684642000</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>2022</v>
       </c>
@@ -11263,7 +11263,7 @@
         <v>64475000000</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>2022</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>2022</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>48567978000</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>2022</v>
       </c>
@@ -11332,7 +11332,7 @@
         <v>5637233000</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>2022</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>133000000</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>2022</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>31746000000</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>2023</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>2023</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>4573766000</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>2023</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>15705000000</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>2023</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>72000000</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>2023</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>4917517000</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>2023</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>16769000000</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>2023</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>2023</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>13209136000</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>2023</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>1625728000</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>2023</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>2023</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>8775000000</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>2023</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>173000000</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>2023</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>4925194000</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>2023</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>17160000000</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>2023</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>595000000</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>2023</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>5014432000</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>2023</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>17353000000</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>2023</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>121000000</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>2023</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>13908113000</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>2023</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>1417778000</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>2023</v>
       </c>
@@ -11855,7 +11855,7 @@
         <v>220000000</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>2023</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>9337000000</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>2023</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>2023</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>4280034000</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>2023</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>18582000000</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>2023</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>417000000</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>2023</v>
       </c>
@@ -11993,7 +11993,7 @@
         <v>5168883000</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>2023</v>
       </c>
@@ -12010,7 +12010,7 @@
         <v>17362000000</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>2023</v>
       </c>
@@ -12033,7 +12033,7 @@
         <v>38000000</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>2023</v>
       </c>
@@ -12050,7 +12050,7 @@
         <v>13769941000</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>2023</v>
       </c>
@@ -12067,7 +12067,7 @@
         <v>1446462000</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>2023</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>301000000</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>2023</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>9697000000</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>2023</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>53000000</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>2023</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>4429826000</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>2023</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>17077000000</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>2023</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>299000000</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>2023</v>
       </c>
@@ -12237,7 +12237,7 @@
         <v>5103665000</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>2023</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>17013000000</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>2023</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>41000000</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>2023</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>14778371000</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>2023</v>
       </c>
@@ -12311,7 +12311,7 @@
         <v>1554043000</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>2023</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>160000000</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>2023</v>
       </c>
@@ -12363,7 +12363,7 @@
         <v>10013000000</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>2023</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>261000000</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>2023</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>18208820000</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>2023</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>68524000000</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>2023</v>
       </c>
@@ -12467,7 +12467,7 @@
         <v>1383000000</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>2023</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>20204497000</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>2023</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>68497000000</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>2023</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>118000000</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>2023</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>55665561000</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>2023</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>6044011000</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>2023</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>681000000</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>2023</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>37822000000</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>2024</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>610559</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>2024</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>4636922000</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>2024</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>15378000000</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>2024</v>
       </c>
@@ -12727,7 +12727,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>2024</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>5050841000</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>2024</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>16313000000</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>2024</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>2024</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>13489019000</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>2024</v>
       </c>
@@ -12830,7 +12830,7 @@
         <v>1892891000</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>2024</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>2024</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>9446000000</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>2024</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>120716144</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>2024</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>4848017000</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>2024</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>18196000000</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>2024</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>519000000</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>2024</v>
       </c>
@@ -13001,7 +13001,7 @@
         <v>5229924000</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>2024</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>16887000000</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>2024</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>2024</v>
       </c>
@@ -13070,7 +13070,7 @@
         <v>14146192000</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>2024</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>1675927000</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>2024</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>185000000</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>2024</v>
       </c>
@@ -13136,7 +13136,7 @@
         <v>10552000000</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>2024</v>
       </c>
@@ -13172,7 +13172,7 @@
         <v>7762816</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>2024</v>
       </c>
@@ -13189,7 +13189,7 @@
         <v>4326870000</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>2024</v>
       </c>
@@ -13206,7 +13206,7 @@
         <v>19847000000</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>2024</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>320000000</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>2024</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>16740000000</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>2024</v>
       </c>
@@ -13293,7 +13293,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>2024</v>
       </c>
@@ -13310,7 +13310,7 @@
         <v>13599535000</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>2024</v>
       </c>
@@ -13327,7 +13327,7 @@
         <v>1530058000</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>2024</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>231000000</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>2024</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>10075000000</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>2024</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>98910482</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>2024</v>
       </c>
@@ -13429,7 +13429,7 @@
         <v>4503058000</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>2024</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>22746000000</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>2024</v>
       </c>
@@ -13481,7 +13481,7 @@
         <v>425000000</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>2024</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>16142000000</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>2024</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>2024</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>11783202000</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>2024</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>1608432000</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>2024</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>294000000</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>2024</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>9798000000</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>2024</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>228000000</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>2024</v>
       </c>
@@ -13671,7 +13671,7 @@
         <v>18314867000</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>2024</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>76167000000</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>2024</v>
       </c>
@@ -13723,7 +13723,7 @@
         <v>1389000000</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>2024</v>
       </c>
@@ -13740,7 +13740,7 @@
         <v>66082000000</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>2024</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>103000000</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>2024</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>53017948000</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>2024</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>6707308000</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>2024</v>
       </c>
@@ -13844,7 +13844,7 @@
         <v>713000000</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>2024</v>
       </c>
@@ -13861,7 +13861,7 @@
         <v>39871000000</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>2025</v>
       </c>
@@ -13897,7 +13897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>2025</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>5305191000</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>2025</v>
       </c>
@@ -13931,7 +13931,7 @@
         <v>21219000000</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>2025</v>
       </c>
@@ -13966,7 +13966,7 @@
         <v>124000000</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>2025</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>15608000000</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>2025</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>2025</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>10824829000</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>2025</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>2020545000</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>2025</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>2025</v>
       </c>
@@ -14101,7 +14101,7 @@
         <v>9949000000</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>2025</v>
       </c>
@@ -14137,7 +14137,7 @@
         <v>35938400</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>2025</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>5629040000</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>2025</v>
       </c>
@@ -14171,7 +14171,7 @@
         <v>24058000000</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>2025</v>
       </c>
@@ -14206,7 +14206,7 @@
         <v>470000000</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>2025</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>16634000000</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>2025</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>2025</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>10761858000</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>2025</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>1571210000</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>2025</v>
       </c>
@@ -14324,7 +14324,7 @@
         <v>188000000</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>2025</v>
       </c>
@@ -14341,7 +14341,7 @@
         <v>10313000000</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>2025</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>4781232</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>2025</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>4769245000</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>2025</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>24447000000</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>2025</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>392000000</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>2025</v>
       </c>
@@ -14463,7 +14463,7 @@
         <v>16884000000</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>2025</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>2025</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>10321665000</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>2025</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>1374519000</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>2025</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>228000000</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>2025</v>
       </c>
@@ -14581,7 +14581,7 @@
         <v>9689000000</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>2025</v>
       </c>
@@ -14617,7 +14617,7 @@
         <v>14280368</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>2025</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>4976429000</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>2025</v>
       </c>
@@ -14651,7 +14651,7 @@
         <v>23238000000</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>2025</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>351000000</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>2025</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>15881000000</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>2025</v>
       </c>
@@ -14738,7 +14738,7 @@
         <v>71000000</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>2025</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>8031601000</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>2025</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>1450556000</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>2025</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>244000000</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>2025</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>9803000000</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>2025</v>
       </c>
@@ -14859,7 +14859,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>2025</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>20679905000</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>2025</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>92962000000</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>2025</v>
       </c>
@@ -14928,7 +14928,7 @@
         <v>1337000000</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>2025</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>65007000000</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>2025</v>
       </c>
@@ -14980,7 +14980,7 @@
         <v>97000000</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>2025</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>39939953000</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>2025</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>6416830000</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>2025</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>704000000</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>2025</v>
       </c>
@@ -15066,7 +15066,7 @@
         <v>39754000000</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>2026</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>2026</v>
       </c>
@@ -15119,7 +15119,7 @@
         <v>4991560000</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>2026</v>
       </c>
@@ -15136,7 +15136,7 @@
         <v>21570000000</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>2026</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>165000000</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>2026</v>
       </c>
@@ -15188,7 +15188,7 @@
         <v>15341000000</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>2026</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>2026</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>1755808000</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>2026</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>59000000</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>2026</v>
       </c>
@@ -15289,7 +15289,7 @@
         <v>9809000000</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>2026</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>2026</v>
       </c>
@@ -15339,7 +15339,7 @@
         <v>6097107000</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>2026</v>
       </c>
@@ -15356,7 +15356,7 @@
         <v>24306000000</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>2026</v>
       </c>
@@ -15391,7 +15391,7 @@
         <v>328000000</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>2026</v>
       </c>
@@ -15408,7 +15408,7 @@
         <v>17170000000</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>2026</v>
       </c>
@@ -15440,7 +15440,7 @@
         <v>53000000</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>2026</v>
       </c>
@@ -15472,7 +15472,7 @@
         <v>90000000</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>2026</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>11103000000</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>2026</v>
       </c>
@@ -15499,8 +15499,32 @@
       <c r="C624" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D624">
+        <v>16335000000</v>
+      </c>
+      <c r="E624">
+        <v>14900000000</v>
+      </c>
+      <c r="F624">
+        <v>16220000000</v>
+      </c>
+      <c r="G624">
+        <v>-269000000</v>
+      </c>
+      <c r="H624">
+        <v>67265000000</v>
+      </c>
+      <c r="I624">
+        <v>80680000000</v>
+      </c>
+      <c r="J624">
+        <v>25395000000</v>
+      </c>
+      <c r="K624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>2026</v>
       </c>
@@ -15511,7 +15535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>2026</v>
       </c>
@@ -15521,8 +15545,14 @@
       <c r="C626" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H626">
+        <v>20733000000</v>
+      </c>
+      <c r="I626">
+        <v>25031000000</v>
+      </c>
+    </row>
+    <row r="627" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>2026</v>
       </c>
@@ -15557,7 +15587,7 @@
         <v>389000000</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>2026</v>
       </c>
@@ -15568,7 +15598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>2026</v>
       </c>
@@ -15578,8 +15608,14 @@
       <c r="C629" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H629">
+        <v>36214000000</v>
+      </c>
+      <c r="I629">
+        <v>45393000000</v>
+      </c>
+    </row>
+    <row r="630" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>2026</v>
       </c>
@@ -15589,8 +15625,29 @@
       <c r="C630" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D630">
+        <v>17875000000</v>
+      </c>
+      <c r="E630">
+        <v>16241000000</v>
+      </c>
+      <c r="F630">
+        <v>16429000000</v>
+      </c>
+      <c r="G630">
+        <v>1029000000</v>
+      </c>
+      <c r="H630">
+        <v>74278000000</v>
+      </c>
+      <c r="I630">
+        <v>88538000000</v>
+      </c>
+      <c r="K630">
+        <v>146000000</v>
+      </c>
+    </row>
+    <row r="631" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>2026</v>
       </c>
@@ -15614,13 +15671,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E8CB36-28FD-4A01-8E6F-FAD97027E6F9}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15637,7 +15694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2013</v>
       </c>
@@ -15654,7 +15711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -15671,7 +15728,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -15688,7 +15745,7 @@
         <v>3600000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -15705,7 +15762,7 @@
         <v>4400000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2017</v>
       </c>
@@ -15722,7 +15779,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -15739,7 +15796,7 @@
         <v>800000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -15756,7 +15813,7 @@
         <v>1100000000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -15773,7 +15830,7 @@
         <v>145000000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2013</v>
       </c>
@@ -15790,7 +15847,7 @@
         <v>250000000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -15807,7 +15864,7 @@
         <v>1100000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2015</v>
       </c>
@@ -15824,7 +15881,7 @@
         <v>2200000000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -15841,7 +15898,7 @@
         <v>2600000000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2017</v>
       </c>
@@ -15858,7 +15915,7 @@
         <v>1700000000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -15875,7 +15932,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2019</v>
       </c>
@@ -15892,7 +15949,7 @@
         <v>2000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -15909,7 +15966,7 @@
         <v>377620000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2013</v>
       </c>
@@ -15926,7 +15983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2014</v>
       </c>
@@ -15943,7 +16000,7 @@
         <v>320000000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2015</v>
       </c>
@@ -15960,7 +16017,7 @@
         <v>1200000000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2016</v>
       </c>
@@ -15977,7 +16034,7 @@
         <v>2600000000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2017</v>
       </c>
@@ -15994,7 +16051,7 @@
         <v>1800000000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -16011,7 +16068,7 @@
         <v>1200000000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2019</v>
       </c>
@@ -16028,7 +16085,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -16053,16 +16110,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490D347E-B079-4188-B046-54C6AF8BB324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16079,7 +16136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -16096,7 +16153,7 @@
         <v>1901355562.5899999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -16113,7 +16170,7 @@
         <v>1082205377.28</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2020</v>
       </c>
@@ -16130,7 +16187,7 @@
         <v>158535000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -16147,7 +16204,7 @@
         <v>83433000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -16164,7 +16221,7 @@
         <v>2293578491.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2021</v>
       </c>

--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F546F10-6DEF-46EB-9646-2E6C2968824B}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E25FA96-0120-4D42-BD6D-72175F9D1F38}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
   <sheets>
     <sheet name="airline_financials" sheetId="2" r:id="rId1"/>
@@ -15614,6 +15614,9 @@
       <c r="I629">
         <v>45393000000</v>
       </c>
+      <c r="K629">
+        <v>62000000</v>
+      </c>
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A630">

--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E25FA96-0120-4D42-BD6D-72175F9D1F38}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488D9128-D1AD-4740-A14E-68235682F4C7}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
   <sheets>
     <sheet name="airline_financials" sheetId="2" r:id="rId1"/>
@@ -15597,6 +15597,12 @@
       <c r="C628" t="s">
         <v>21</v>
       </c>
+      <c r="H628">
+        <v>14439000000</v>
+      </c>
+      <c r="I628">
+        <v>17268000000</v>
+      </c>
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A629">

--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488D9128-D1AD-4740-A14E-68235682F4C7}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC9621AF-35C5-4ECC-88E0-5A11EC00DE4D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
   <sheets>
     <sheet name="airline_financials" sheetId="2" r:id="rId1"/>
@@ -985,22 +985,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BF35CD-6CF2-4D2E-9294-3A1A732D8FBE}">
   <dimension ref="A1:K631"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2014</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>2381139000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2014</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>8352000000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2014</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>99000000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>4038973000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2014</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>10419000000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2014</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>29000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2014</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>3784727000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2014</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>2777000000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2014</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2014</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>2289201000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2014</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>8988000000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2014</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>340000000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2014</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>4262774000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2014</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>11386000000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2014</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2014</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>4008507000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2014</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>78000000</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2014</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>3202000000</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2014</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2014</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>2106214000</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2014</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>9582000000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2014</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>384000000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2014</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>4502856000</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2014</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>11752000000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2014</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2014</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>4174397000</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2014</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>103000000</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2014</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>3217000000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2014</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2014</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>2169062000</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2014</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>9156000000</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2014</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>262000000</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2014</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>4269027000</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2014</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>11437000000</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2014</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2014</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>4372511000</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2014</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2014</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>3044000000</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2014</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2014</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>8945616000</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2014</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>36078000000</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2014</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>1085000000</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2014</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>17073630000</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2014</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>44994000000</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2014</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>355000000</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2014</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>16340142000</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2014</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>235000000</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2014</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>12240000000</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2015</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2015</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2526031000</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2015</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>9257000000</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2015</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>136000000</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2015</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>4229686000</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2015</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>11419000000</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2015</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>126000000</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2015</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>4729463000</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2015</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2015</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>2819000000</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2015</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2015</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>2690457000</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2015</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>9949000000</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2015</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>411000000</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2015</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>4441648000</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2015</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>12237000000</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2015</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>182000000</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2015</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>5213299000</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2015</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>195000000</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2015</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>3200000000</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2015</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2015</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2597658000</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2015</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>10368000000</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2015</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>563000000</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2015</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>4663198000</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2015</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>12976000000</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2015</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>177000000</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2015</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>5597997000</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2015</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>257000000</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2015</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>3315000000</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2015</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2015</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>2712464000</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2015</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>10340000000</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2015</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>380000000</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2015</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>4391790000</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2015</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>12626000000</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2015</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>136000000</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2015</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>5705397000</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2015</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>146000000</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2015</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>3357000000</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2015</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2015</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>10526610000</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2015</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>39914000000</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2015</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>1490000000</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2015</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>17726322000</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2015</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>49258000000</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2015</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>620000000</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2015</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>21246156000</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2015</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>698000000</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2015</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>12691000000</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2016</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2016</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>3001384000</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2016</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>10453000000</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2016</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>272000000</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2016</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>4368096000</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2016</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>13029000000</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2016</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>155000000</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2016</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>5983005000</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2016</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>94000000</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2016</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>3265000000</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2016</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>98000000</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2016</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>3178904000</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2016</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>11062000000</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2016</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>324000000</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2016</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>4551094000</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2016</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>13597000000</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2016</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>206000000</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2016</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>6419419000</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2016</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>153000000</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2016</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>3689000000</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2016</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>86000000</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2016</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>3121762000</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2016</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>11212000000</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2016</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>326000000</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2016</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>4894768000</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2016</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>13796000000</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2016</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>101000000</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2016</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>6507204000</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2016</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>235000000</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2016</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>3867000000</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2016</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>57000000</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2016</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>3073455000</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2016</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>11408000000</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2016</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>193000000</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2016</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>4570679000</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2016</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>13198000000</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2016</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>123000000</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2016</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>6585017000</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2016</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>145000000</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2016</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>314000000</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2016</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>12375505000</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2016</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>44135000000</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2016</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>1115000000</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2016</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>18384637000</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2016</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>53620000000</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2016</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>586000000</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2016</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>25494645000</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2016</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>628000000</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2017</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2017</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>3376837000</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2017</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>14394000000</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2017</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>151000000</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2017</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>4522353000</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2017</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>13580000000</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2017</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>99000000</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2017</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>6875899000</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2017</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2017</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>94000000</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2017</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>3584209000</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2017</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>15612000000</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2017</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>338000000</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2017</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>4735491000</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2017</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>14246000000</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2017</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>202000000</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2017</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>7294578000</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2017</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>140000000</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2017</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2017</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>3220246000</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2017</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>16164000000</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2017</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>314000000</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2017</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>4950800000</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2017</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>14306000000</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2017</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2017</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>7681312000</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2017</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>109000000</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2017</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>47000000</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2017</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>3430711000</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2017</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>15902000000</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2017</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>262000000</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2017</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>4798038000</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2017</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>13875000000</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2017</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>115000000</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2017</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>7741030000</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2017</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2017</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>241000000</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2017</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>13612003000</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2017</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>62072000000</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2017</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>1065000000</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2017</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>19006682000</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2017</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>56007000000</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2017</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>543000000</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2017</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>29592819000</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2017</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>349000000</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2018</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>29000000</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2018</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>3728563000</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2018</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>15480000000</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2018</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>188000000</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2018</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>4731498000</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2018</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>14025000000</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2018</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>102000000</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2018</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>8408764000</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2018</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>17000000</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2018</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>63000000</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2018</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>3922294000</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2018</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>16833000000</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2018</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>404000000</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2018</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>5020026000</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2018</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>15138000000</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2018</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>166000000</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2018</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>9515842000</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2018</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>108000000</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2018</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2018</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>3643948000</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2018</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>16943000000</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2018</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>399000000</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2018</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>5352976000</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2018</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>15551000000</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2018</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>135000000</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2018</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>9579448000</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2018</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2018</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2018</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>3605069000</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2018</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>16079000000</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2018</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>311000000</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2018</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>5067411000</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2018</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>15167000000</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2018</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>141000000</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2018</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>8998928000</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2018</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>82000000</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2018</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>175000000</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2018</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>14899874000</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2018</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>65335000000</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2018</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>1301000000</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2018</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>20171911000</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>2018</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>59881000000</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>2018</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>544000000</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>2018</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>36502982000</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>2018</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>334000000</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>2019</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2019</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>3802132000</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2019</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>15508000000</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2019</v>
       </c>
@@ -6706,7 +6706,7 @@
         <v>220000000</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2019</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>4851921000</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>2019</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>15437000000</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2019</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>88000000</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>2019</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>9829044000</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>2019</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>33000000</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2019</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>67000000</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2019</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>4311182000</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2019</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>16980000000</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2019</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>518000000</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>2019</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>5157677000</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>2019</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>16029000000</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2019</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>170000000</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>2019</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>10775878000</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2019</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>161000000</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2019</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>52000000</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2019</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>3687473000</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2019</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>17519000000</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>2019</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>517000000</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>2019</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>5331914000</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>2019</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>16296000000</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>2019</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>144000000</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2019</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>10686246000</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2019</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>174000000</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2019</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>74000000</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2019</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>3745031000</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>2019</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>16647000000</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>2019</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>387000000</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>2019</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>5255199000</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>2019</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>16079000000</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>2019</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>264000000</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>2019</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>10491833000</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>2019</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>123000000</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>2019</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>213000000</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>2019</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>15545818000</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>2019</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>66654000000</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2019</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>1643000000</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>2019</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>20596711000</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>2019</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>63841000000</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>2019</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>667000000</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2019</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>41783001000</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>2019</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>491000000</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>2020</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>2020</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>3964009000</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>2020</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>15304000000</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>2020</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>2020</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>4979529000</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>2020</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>14891000000</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2020</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>2020</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>10913934000</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>2020</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>1508196000</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>2020</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>2020</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>7140000000</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>2020</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>2020</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>2174683000</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>2020</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>4307000000</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>2020</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>2020</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>409490000</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>2020</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>2413000000</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>2020</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>2020</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>1809874000</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>2020</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>318049000</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>2020</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>2020</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>1549000000</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>2020</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>2020</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>3449339000</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>2020</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>7871000000</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>2020</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>2020</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>718405000</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>2020</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>6905000000</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>2020</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>2020</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>7164634000</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2020</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>763362000</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>2020</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>2020</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>3986000000</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>2020</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>2020</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>3226049000</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>2020</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>9632000000</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>2020</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>2020</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>1453062000</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>2020</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>8480000000</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>2020</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>2020</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>7829945000</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>2020</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>876634000</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>2020</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>2020</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>4280000000</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>2020</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>2020</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>12814080000</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>2020</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>37114000000</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>2020</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>2020</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>7560486000</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>2020</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>32689000000</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>2020</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>2020</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>27718387000</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>2020</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>3466240000</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>2020</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>2020</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>16955000000</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>2021</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>2021</v>
       </c>
@@ -8960,7 +8960,7 @@
         <v>3921090000</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>2021</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>10397000000</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>2021</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>2021</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>2481647000</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>2021</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>9090000000</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>2021</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>24000000</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>2021</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>7976158000</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>2021</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>1158012000</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>2021</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>2021</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>4592000000</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>2021</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>2021</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>4505786000</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>2021</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>13413000000</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>2021</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>2021</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>3586928000</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>2021</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>13645000000</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>2021</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>85000000</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>2021</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>10226746000</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>2021</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>1198768000</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>2021</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>2021</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>6934000000</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>2021</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>2021</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>4312893000</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>2021</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>14429000000</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>2021</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>2021</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>4229461000</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>2021</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>16168000000</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>2021</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>77000000</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2021</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>11059710000</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>2021</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>1296555000</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>2021</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>2021</v>
       </c>
@@ -9640,7 +9640,7 @@
         <v>7505000000</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>2021</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>2021</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>4288133000</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>2021</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>14206000000</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>2021</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>2021</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>4237389000</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>2021</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>15210000000</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>2021</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>2021</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>11486720000</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>2021</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>1190868000</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>2021</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>2021</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>7836000000</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>2021</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>2021</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>17027902000</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>2021</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>52445000000</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>2021</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>2021</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>14535425000</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>2021</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>54113000000</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>2021</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>230000000</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>2021</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>40749334000</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>2021</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>4844203000</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>2021</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>2021</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>26867000000</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>2022</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>2022</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>4512315000</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>2022</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>13783000000</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>2022</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>2022</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>4263048000</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>2022</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>15383000000</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>2022</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>37000000</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>2022</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>11718896000</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>2022</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>1684532000</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>2022</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2022</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>7442000000</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2022</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>64000000</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>2022</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>4888539000</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2022</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>15611000000</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>2022</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>2022</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>4516296000</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>2022</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>16405000000</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>2022</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>2022</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>11846547000</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2022</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>1343116000</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>2022</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2022</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>7594000000</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2022</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>59000000</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2022</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>4315984000</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2022</v>
       </c>
@@ -10703,7 +10703,7 @@
         <v>16349000000</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>2022</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>237000000</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>2022</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>4964785000</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>2022</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>16217000000</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>2022</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>57000000</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>2022</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>12131033000</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>2022</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>1256755000</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>2022</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>2022</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>8040000000</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>2022</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>88000000</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>2022</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>4192352000</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>2022</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>15030000000</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>2022</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>272000000</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>2022</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>4940513000</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>2022</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>16470000000</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>2022</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>49000000</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>2022</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>12871502000</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>2022</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>1352830000</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>2022</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>2022</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>8670000000</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>2022</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>211000000</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>2022</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>17909190000</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>2022</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>60773000000</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>2022</v>
       </c>
@@ -11229,7 +11229,7 @@
         <v>563000000</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>2022</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>18684642000</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>2022</v>
       </c>
@@ -11263,7 +11263,7 @@
         <v>64475000000</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>2022</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>2022</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>48567978000</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>2022</v>
       </c>
@@ -11332,7 +11332,7 @@
         <v>5637233000</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>2022</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>133000000</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>2022</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>31746000000</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>2023</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>2023</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>4573766000</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>2023</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>15705000000</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>2023</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>72000000</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>2023</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>4917517000</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>2023</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>16769000000</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>2023</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>2023</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>13209136000</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>2023</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>1625728000</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>2023</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>2023</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>8775000000</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>2023</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>173000000</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>2023</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>4925194000</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>2023</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>17160000000</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>2023</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>595000000</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>2023</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>5014432000</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>2023</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>17353000000</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>2023</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>121000000</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>2023</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>13908113000</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>2023</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>1417778000</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>2023</v>
       </c>
@@ -11855,7 +11855,7 @@
         <v>220000000</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>2023</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>9337000000</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>2023</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>2023</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>4280034000</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>2023</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>18582000000</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>2023</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>417000000</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>2023</v>
       </c>
@@ -11993,7 +11993,7 @@
         <v>5168883000</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>2023</v>
       </c>
@@ -12010,7 +12010,7 @@
         <v>17362000000</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>2023</v>
       </c>
@@ -12033,7 +12033,7 @@
         <v>38000000</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>2023</v>
       </c>
@@ -12050,7 +12050,7 @@
         <v>13769941000</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>2023</v>
       </c>
@@ -12067,7 +12067,7 @@
         <v>1446462000</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>2023</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>301000000</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>2023</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>9697000000</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>2023</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>53000000</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>2023</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>4429826000</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>2023</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>17077000000</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>2023</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>299000000</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>2023</v>
       </c>
@@ -12237,7 +12237,7 @@
         <v>5103665000</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>2023</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>17013000000</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>2023</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>41000000</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>2023</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>14778371000</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>2023</v>
       </c>
@@ -12311,7 +12311,7 @@
         <v>1554043000</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>2023</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>160000000</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>2023</v>
       </c>
@@ -12363,7 +12363,7 @@
         <v>10013000000</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>2023</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>261000000</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>2023</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>18208820000</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>2023</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>68524000000</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>2023</v>
       </c>
@@ -12467,7 +12467,7 @@
         <v>1383000000</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>2023</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>20204497000</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>2023</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>68497000000</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>2023</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>118000000</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>2023</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>55665561000</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>2023</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>6044011000</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>2023</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>681000000</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>2023</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>37822000000</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>2024</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>610559</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>2024</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>4636922000</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>2024</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>15378000000</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>2024</v>
       </c>
@@ -12727,7 +12727,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>2024</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>5050841000</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>2024</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>16313000000</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>2024</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>2024</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>13489019000</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>2024</v>
       </c>
@@ -12830,7 +12830,7 @@
         <v>1892891000</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>2024</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>2024</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>9446000000</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>2024</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>120716144</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>2024</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>4848017000</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>2024</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>18196000000</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>2024</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>519000000</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>2024</v>
       </c>
@@ -13001,7 +13001,7 @@
         <v>5229924000</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>2024</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>16887000000</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>2024</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>2024</v>
       </c>
@@ -13070,7 +13070,7 @@
         <v>14146192000</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>2024</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>1675927000</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>2024</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>185000000</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>2024</v>
       </c>
@@ -13136,7 +13136,7 @@
         <v>10552000000</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>2024</v>
       </c>
@@ -13172,7 +13172,7 @@
         <v>7762816</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>2024</v>
       </c>
@@ -13189,7 +13189,7 @@
         <v>4326870000</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>2024</v>
       </c>
@@ -13206,7 +13206,7 @@
         <v>19847000000</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>2024</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>320000000</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>2024</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>16740000000</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>2024</v>
       </c>
@@ -13293,7 +13293,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>2024</v>
       </c>
@@ -13310,7 +13310,7 @@
         <v>13599535000</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>2024</v>
       </c>
@@ -13327,7 +13327,7 @@
         <v>1530058000</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>2024</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>231000000</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>2024</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>10075000000</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>2024</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>98910482</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>2024</v>
       </c>
@@ -13429,7 +13429,7 @@
         <v>4503058000</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>2024</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>22746000000</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>2024</v>
       </c>
@@ -13481,7 +13481,7 @@
         <v>425000000</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>2024</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>16142000000</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>2024</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>2024</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>11783202000</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>2024</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>1608432000</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>2024</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>294000000</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>2024</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>9798000000</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>2024</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>228000000</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>2024</v>
       </c>
@@ -13671,7 +13671,7 @@
         <v>18314867000</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>2024</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>76167000000</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>2024</v>
       </c>
@@ -13723,7 +13723,7 @@
         <v>1389000000</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>2024</v>
       </c>
@@ -13740,7 +13740,7 @@
         <v>66082000000</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>2024</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>103000000</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>2024</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>53017948000</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>2024</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>6707308000</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>2024</v>
       </c>
@@ -13844,7 +13844,7 @@
         <v>713000000</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>2024</v>
       </c>
@@ -13861,7 +13861,7 @@
         <v>39871000000</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>2025</v>
       </c>
@@ -13897,7 +13897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>2025</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>5305191000</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>2025</v>
       </c>
@@ -13931,7 +13931,7 @@
         <v>21219000000</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>2025</v>
       </c>
@@ -13966,7 +13966,7 @@
         <v>124000000</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>2025</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>15608000000</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>2025</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>2025</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>10824829000</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>2025</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>2020545000</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>2025</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>2025</v>
       </c>
@@ -14101,7 +14101,7 @@
         <v>9949000000</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>2025</v>
       </c>
@@ -14137,7 +14137,7 @@
         <v>35938400</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>2025</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>5629040000</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>2025</v>
       </c>
@@ -14171,7 +14171,7 @@
         <v>24058000000</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>2025</v>
       </c>
@@ -14206,7 +14206,7 @@
         <v>470000000</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>2025</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>16634000000</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>2025</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>2025</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>10761858000</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>2025</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>1571210000</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>2025</v>
       </c>
@@ -14324,7 +14324,7 @@
         <v>188000000</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>2025</v>
       </c>
@@ -14341,7 +14341,7 @@
         <v>10313000000</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>2025</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>4781232</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>2025</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>4769245000</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>2025</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>24447000000</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>2025</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>392000000</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>2025</v>
       </c>
@@ -14463,7 +14463,7 @@
         <v>16884000000</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>2025</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>2025</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>10321665000</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>2025</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>1374519000</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>2025</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>228000000</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>2025</v>
       </c>
@@ -14581,7 +14581,7 @@
         <v>9689000000</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>2025</v>
       </c>
@@ -14617,7 +14617,7 @@
         <v>14280368</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>2025</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>4976429000</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>2025</v>
       </c>
@@ -14651,7 +14651,7 @@
         <v>23238000000</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>2025</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>351000000</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>2025</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>15881000000</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>2025</v>
       </c>
@@ -14738,7 +14738,7 @@
         <v>71000000</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>2025</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>8031601000</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>2025</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>1450556000</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>2025</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>244000000</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>2025</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>9803000000</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>2025</v>
       </c>
@@ -14859,7 +14859,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>2025</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>20679905000</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>2025</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>92962000000</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>2025</v>
       </c>
@@ -14928,7 +14928,7 @@
         <v>1337000000</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>2025</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>65007000000</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>2025</v>
       </c>
@@ -14980,7 +14980,7 @@
         <v>97000000</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>2025</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>39939953000</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>2025</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>6416830000</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>2025</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>704000000</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>2025</v>
       </c>
@@ -15066,7 +15066,7 @@
         <v>39754000000</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>2026</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>2026</v>
       </c>
@@ -15119,7 +15119,7 @@
         <v>4991560000</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>2026</v>
       </c>
@@ -15136,7 +15136,7 @@
         <v>21570000000</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>2026</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>165000000</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>2026</v>
       </c>
@@ -15188,7 +15188,7 @@
         <v>15341000000</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>2026</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>2026</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>1755808000</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>2026</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>59000000</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>2026</v>
       </c>
@@ -15289,7 +15289,7 @@
         <v>9809000000</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>2026</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>2026</v>
       </c>
@@ -15339,7 +15339,7 @@
         <v>6097107000</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>2026</v>
       </c>
@@ -15356,7 +15356,7 @@
         <v>24306000000</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>2026</v>
       </c>
@@ -15391,7 +15391,7 @@
         <v>328000000</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>2026</v>
       </c>
@@ -15408,7 +15408,7 @@
         <v>17170000000</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>2026</v>
       </c>
@@ -15440,7 +15440,7 @@
         <v>53000000</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>2026</v>
       </c>
@@ -15472,7 +15472,7 @@
         <v>90000000</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>2026</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>11103000000</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>2026</v>
       </c>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>2026</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>2026</v>
       </c>
@@ -15552,7 +15552,7 @@
         <v>25031000000</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>2026</v>
       </c>
@@ -15587,7 +15587,7 @@
         <v>389000000</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>2026</v>
       </c>
@@ -15604,7 +15604,7 @@
         <v>17268000000</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>2026</v>
       </c>
@@ -15624,7 +15624,7 @@
         <v>62000000</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>2026</v>
       </c>
@@ -15656,7 +15656,7 @@
         <v>146000000</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>2026</v>
       </c>
@@ -15665,6 +15665,12 @@
       </c>
       <c r="C631" t="s">
         <v>25</v>
+      </c>
+      <c r="H631">
+        <v>9000000000</v>
+      </c>
+      <c r="I631">
+        <v>11419000000</v>
       </c>
     </row>
   </sheetData>
@@ -15680,13 +15686,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E8CB36-28FD-4A01-8E6F-FAD97027E6F9}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15703,7 +15709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2013</v>
       </c>
@@ -15720,7 +15726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -15737,7 +15743,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -15754,7 +15760,7 @@
         <v>3600000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -15771,7 +15777,7 @@
         <v>4400000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2017</v>
       </c>
@@ -15788,7 +15794,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -15805,7 +15811,7 @@
         <v>800000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -15822,7 +15828,7 @@
         <v>1100000000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -15839,7 +15845,7 @@
         <v>145000000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2013</v>
       </c>
@@ -15856,7 +15862,7 @@
         <v>250000000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -15873,7 +15879,7 @@
         <v>1100000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2015</v>
       </c>
@@ -15890,7 +15896,7 @@
         <v>2200000000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -15907,7 +15913,7 @@
         <v>2600000000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2017</v>
       </c>
@@ -15924,7 +15930,7 @@
         <v>1700000000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -15941,7 +15947,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2019</v>
       </c>
@@ -15958,7 +15964,7 @@
         <v>2000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -15975,7 +15981,7 @@
         <v>377620000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2013</v>
       </c>
@@ -15992,7 +15998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2014</v>
       </c>
@@ -16009,7 +16015,7 @@
         <v>320000000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2015</v>
       </c>
@@ -16026,7 +16032,7 @@
         <v>1200000000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2016</v>
       </c>
@@ -16043,7 +16049,7 @@
         <v>2600000000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2017</v>
       </c>
@@ -16060,7 +16066,7 @@
         <v>1800000000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -16077,7 +16083,7 @@
         <v>1200000000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2019</v>
       </c>
@@ -16094,7 +16100,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -16119,16 +16125,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490D347E-B079-4188-B046-54C6AF8BB324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16145,7 +16151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -16162,7 +16168,7 @@
         <v>1901355562.5899999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -16179,7 +16185,7 @@
         <v>1082205377.28</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2020</v>
       </c>
@@ -16196,7 +16202,7 @@
         <v>158535000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -16213,7 +16219,7 @@
         <v>83433000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -16230,7 +16236,7 @@
         <v>2293578491.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
